--- a/活动兑换.xlsx
+++ b/活动兑换.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unlight\Unlight_Revive\Announcements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED141220-60CF-477B-846C-1184453ABDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F0E80F-244D-4BBD-BFA3-BF1E79B86214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19605" yWindow="5310" windowWidth="15405" windowHeight="14205" xr2:uid="{DC22B4BA-6B94-41B8-935E-265380A15134}"/>
+    <workbookView xWindow="18750" yWindow="4515" windowWidth="15405" windowHeight="14205" xr2:uid="{DC22B4BA-6B94-41B8-935E-265380A15134}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
     <t>道具</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -243,20 +243,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>移1特1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移2特2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>移3特3</t>
+    <t>*GEM开放兑换时间：*&lt;br&gt;*活动结束后  ～ 2026/2/26定期维护前*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>バレンタインカード  &lt;a href="imgs/costumes/レインディアブーツ（白</t>
+      <t>ホワイトローラー</t>
     </r>
     <r>
       <rPr>
@@ -266,7 +258,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>・青・赤）</t>
+      <t>&lt;br&gt;*</t>
     </r>
     <r>
       <rPr>
@@ -275,15 +267,8 @@
         <rFont val="等线"/>
         <family val="2"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
-      <t>_Preview.jpg"  target="_blank"&gt;[预览]&lt;/a&gt;&lt;br&gt;*情人节卡片*</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>高級チョコレート  &lt;a href="imgs/costumes/レインディアブーツ（白</t>
+      <t>白色擀面杖</t>
     </r>
     <r>
       <rPr>
@@ -293,23 +278,34 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>・青・赤）</t>
+      <t>*</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>_Preview.jpg"  target="_blank"&gt;[预览]&lt;/a&gt;&lt;br&gt;*高级巧克力*</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>*GEM开放兑换时间：*&lt;br&gt;*活动结束后  ～ 2026/2/26定期维护前*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒杯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>盾3移1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>盾4移1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>盾5移1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ニューイヤードレス(黄)  &lt;a href="imgs/costumes/レインディアブーツ（白・青・赤）_Preview.jpg"  target="_blank"&gt;[预览]&lt;/a&gt;&lt;br&gt;*情人节卡片*</t>
+  </si>
+  <si>
+    <t>ニューイヤーシューズ(黃)  &lt;a href="imgs/costumes/レインディアブーツ（白・青・赤）_Preview.jpg"  target="_blank"&gt;[预览]&lt;/a&gt;&lt;br&gt;*高级巧克力*</t>
+  </si>
+  <si>
+    <t>ロング(灰)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -317,7 +313,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +342,13 @@
       <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1067,61 +1070,79 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31">
+        <v>60</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
       <c r="D31">
         <f t="shared" ref="D31:D35" si="2">B31*C31</f>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <f t="shared" si="2"/>
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34">
         <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35">
         <v>65</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C35">
+        <v>1</v>
+      </c>
       <c r="D35">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -1130,7 +1151,7 @@
       </c>
       <c r="D36" t="str">
         <f>"*"&amp;SUM(D31:D35)&amp;"*"</f>
-        <v>*235*</v>
+        <v>*355*</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -1151,21 +1172,48 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41">
+        <v>30</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
       <c r="D41">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42">
+        <v>30</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
       <c r="D42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43">
+        <v>30</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
       <c r="D43">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -1198,34 +1246,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49">
-        <v>30</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D49">
         <f t="shared" si="4"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50">
-        <v>30</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D50">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -1234,7 +1264,7 @@
       </c>
       <c r="D51" t="str">
         <f>"*"&amp;SUM(D39:D50)&amp;"*"</f>
-        <v>*60*</v>
+        <v>*90*</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -1288,7 +1318,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -1297,7 +1327,7 @@
       </c>
       <c r="D60">
         <f>MID(D28,2,LEN(D28)-2)+MID(D36,2,LEN(D36)-2)+MID(D51,2,LEN(D51)-2)</f>
-        <v>1028</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -1315,7 +1345,7 @@
       </c>
       <c r="D62">
         <f>D60-D61</f>
-        <v>818</v>
+        <v>968</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -1324,7 +1354,7 @@
       </c>
       <c r="D63">
         <f>ROUNDUP(D62/5,0)*3</f>
-        <v>492</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
